--- a/diseases/d122/2005-2009.xlsx
+++ b/diseases/d122/2005-2009.xlsx
@@ -10992,11 +10992,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_TRIC_ANNUAL</t>
@@ -11014,12 +11009,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -11029,11 +11019,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11099,17 +11084,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11143,39 +11128,17 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.1487818762845223</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11183,64 +11146,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11248,27 +11153,17 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
         <v>1</v>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -11276,7 +11171,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -11296,7 +11191,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -11338,12 +11233,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11368,31 +11263,28 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007-02-12</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.1487818762845223</v>
+        <v>3</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11407,7 +11299,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11415,42 +11307,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11374,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11512,19 +11404,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2007-02-12</t>
+          <t>2007-04-23</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -11623,12 +11515,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>DE-HH</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11653,19 +11545,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2007-04-23</t>
+          <t>2007-07-09</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -11764,12 +11656,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11794,19 +11686,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>2007-08-06</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -11905,12 +11797,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>DE-NI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Niedersachsen, Germany</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11935,12 +11827,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2007-08-06</t>
+          <t>2007-09-03</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12046,12 +11938,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DE-NI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Niedersachsen, Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12076,28 +11968,31 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2007-09-03</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
+          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12112,7 +12007,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
+          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -12120,42 +12015,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12082,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12226,17 +12121,17 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>0.04668661585762263</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12256,7 +12151,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12264,42 +12159,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12226,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12370,17 +12265,17 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="O83" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="R83" t="n">
-        <v>0.04668661585762263</v>
+        <v>0.8891140131468114</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12400,7 +12295,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -12413,7 +12308,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -12433,7 +12328,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -12475,12 +12370,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12514,17 +12409,17 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.8891140131468114</v>
+        <v>0</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12544,7 +12439,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -12557,7 +12452,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -12577,7 +12472,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -12619,12 +12514,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12668,7 +12563,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12688,7 +12583,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -12701,7 +12596,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -12721,7 +12616,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -12763,12 +12658,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12802,17 +12697,17 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>0.001232881798388405</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
+          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12832,7 +12727,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
+          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -12840,42 +12735,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12802,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12946,17 +12841,17 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.001232881798388405</v>
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12976,7 +12871,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -12984,42 +12879,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13051,12 +12946,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13090,17 +12985,17 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>0.05839724984424156</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13120,7 +13015,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13133,7 +13028,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -13153,7 +13048,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -13195,12 +13090,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13234,17 +13129,17 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.05839724984424156</v>
+        <v>0</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13264,7 +13159,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -13272,42 +13167,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13339,12 +13234,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13378,17 +13273,17 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>0.004778577446165741</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13408,7 +13303,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -13416,42 +13311,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13483,12 +13378,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13522,17 +13417,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.004778577446165741</v>
+        <v>0</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13552,7 +13447,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -13565,7 +13460,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -13585,7 +13480,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -13627,12 +13522,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13676,7 +13571,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13696,7 +13591,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -13709,7 +13604,7 @@
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
@@ -13729,7 +13624,7 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
@@ -13771,12 +13666,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13810,17 +13705,17 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.04991685349712983</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13840,7 +13735,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -13853,7 +13748,7 @@
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -13873,7 +13768,7 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
@@ -13915,12 +13810,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13954,17 +13849,17 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.04991685349712983</v>
+        <v>0</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13984,7 +13879,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -13992,42 +13887,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -14059,12 +13954,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14108,7 +14003,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -14128,7 +14023,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -14136,42 +14031,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -14203,12 +14098,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14252,7 +14147,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14272,7 +14167,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -14285,7 +14180,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -14305,7 +14200,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -14347,12 +14242,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14386,17 +14281,17 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.9692102234170257</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14416,7 +14311,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -14429,7 +14324,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -14449,7 +14344,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -14491,12 +14386,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14530,17 +14425,17 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.9692102234170257</v>
+        <v>0</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -14560,7 +14455,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -14573,7 +14468,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -14593,7 +14488,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -14635,12 +14530,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14674,17 +14569,17 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>0.1836790594162725</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -14704,7 +14599,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -14717,7 +14612,7 @@
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
@@ -14737,7 +14632,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -14779,12 +14674,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -14818,17 +14713,17 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.1836790594162725</v>
+        <v>0</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
+          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -14848,7 +14743,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
+          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -14861,7 +14756,7 @@
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -14881,7 +14776,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -14923,12 +14818,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14962,17 +14857,17 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>0.006025091614530544</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -14992,7 +14887,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -15005,7 +14900,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -15025,7 +14920,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -15067,12 +14962,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15106,17 +15001,17 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.006025091614530544</v>
+        <v>0</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -15126,7 +15021,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
@@ -15136,7 +15031,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -15144,42 +15039,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15211,12 +15106,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15255,12 +15150,9 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -15270,7 +15162,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
@@ -15280,7 +15172,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -15288,42 +15180,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15355,12 +15247,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15496,12 +15388,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15637,12 +15529,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -15778,12 +15670,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -15919,12 +15811,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16060,12 +15952,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16201,12 +16093,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16342,12 +16234,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16483,12 +16375,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -16624,12 +16516,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -16765,12 +16657,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16906,12 +16798,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17047,12 +16939,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17188,12 +17080,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17329,12 +17221,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -17470,12 +17362,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -17611,12 +17503,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -17752,12 +17644,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -17893,12 +17785,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -17932,14 +17824,17 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.0105274510919625</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -17959,7 +17854,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -17967,42 +17862,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -18034,12 +17929,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -18073,17 +17968,17 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0.0105274510919625</v>
+        <v>0</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -18103,7 +17998,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -18116,7 +18011,7 @@
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
@@ -18136,7 +18031,7 @@
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
@@ -18178,12 +18073,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -18217,17 +18112,17 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.427753576930491</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -18247,7 +18142,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -18260,7 +18155,7 @@
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
@@ -18280,7 +18175,7 @@
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
@@ -18322,12 +18217,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -18361,17 +18256,17 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>503</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>503</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>2.427753576930491</v>
+        <v>0.04938063108940338</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -18391,7 +18286,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -18404,7 +18299,7 @@
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
@@ -18424,7 +18319,7 @@
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
@@ -18466,12 +18361,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -18505,22 +18400,17 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R126" t="n">
-        <v>0.04938063108940338</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.3346271941667787</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -18535,27 +18425,17 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT126" t="n">
         <v>1</v>
       </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -18563,7 +18443,7 @@
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
@@ -18583,7 +18463,7 @@
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
@@ -18620,17 +18500,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -18655,12 +18535,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-02-11</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -18671,96 +18551,13 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -18769,65 +18566,55 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AT127" t="n">
         <v>1</v>
       </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18646,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -18889,26 +18676,26 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.3346271941667787</v>
+        <v>0</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
+          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -18928,7 +18715,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
+          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -18936,42 +18723,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
     </row>
@@ -19003,12 +18790,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -19033,28 +18820,31 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2008-02-11</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
+          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -19069,7 +18859,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
+          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -19077,42 +18867,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -19144,12 +18934,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -19183,17 +18973,17 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>5.435354900296294</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -19213,7 +19003,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -19221,42 +19011,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -19288,12 +19078,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -19337,7 +19127,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -19357,7 +19147,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -19370,7 +19160,7 @@
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
@@ -19390,7 +19180,7 @@
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
@@ -19432,12 +19222,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -19471,17 +19261,17 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>5.435354900296294</v>
+        <v>0</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -19501,7 +19291,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TRIC_ANNUAL</t>
+          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -19514,7 +19304,7 @@
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
@@ -19534,7 +19324,7 @@
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
@@ -19576,12 +19366,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -19615,17 +19405,17 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>0.001235555079235344</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19645,7 +19435,7 @@
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -19653,42 +19443,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -19720,12 +19510,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -19769,7 +19559,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
+          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19789,7 +19579,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TRIC_ANNUAL</t>
+          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -19802,7 +19592,7 @@
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
@@ -19822,7 +19612,7 @@
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
@@ -19864,12 +19654,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -19903,17 +19693,17 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R135" t="n">
-        <v>0.001235555079235344</v>
+        <v>0.01501012754748668</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19933,7 +19723,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -19941,42 +19731,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20008,12 +19798,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -20057,7 +19847,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -20077,7 +19867,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -20085,42 +19875,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20152,12 +19942,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -20191,17 +19981,17 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O137" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R137" t="n">
-        <v>0.01501012754748668</v>
+        <v>0.01426161374311218</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -20221,7 +20011,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TRIC_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -20234,7 +20024,7 @@
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
@@ -20254,7 +20044,7 @@
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
@@ -20296,12 +20086,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -20345,7 +20135,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -20365,7 +20155,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -20373,42 +20163,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20440,12 +20230,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -20479,17 +20269,17 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O139" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>0.01426161374311218</v>
+        <v>0.01800492956966688</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -20509,7 +20299,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -20522,7 +20312,7 @@
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
@@ -20542,7 +20332,7 @@
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
@@ -20584,12 +20374,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -20623,17 +20413,17 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.08998759970876014</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
+          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -20653,7 +20443,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TRIC_ANNUAL</t>
+          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -20666,7 +20456,7 @@
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
@@ -20686,7 +20476,7 @@
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
@@ -20728,12 +20518,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -20767,17 +20557,17 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.01800492956966688</v>
+        <v>0</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -20797,7 +20587,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -20805,42 +20595,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -20872,12 +20662,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -20911,17 +20701,17 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>0.08998759970876014</v>
+        <v>0.001669337314235413</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -20941,7 +20731,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -20954,7 +20744,7 @@
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
@@ -20974,7 +20764,7 @@
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
@@ -21016,12 +20806,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -21055,17 +20845,17 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>0.6322603243369012</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -21085,7 +20875,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -21093,42 +20883,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21160,12 +20950,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -21199,17 +20989,17 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.001669337314235413</v>
+        <v>0</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -21229,7 +21019,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -21242,7 +21032,7 @@
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
@@ -21262,7 +21052,7 @@
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
@@ -21304,12 +21094,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -21343,17 +21133,17 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O145" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R145" t="n">
-        <v>0.6322603243369012</v>
+        <v>0.420159730724297</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -21373,7 +21163,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -21386,7 +21176,7 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
@@ -21406,7 +21196,7 @@
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
@@ -21448,12 +21238,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -21497,7 +21287,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -21517,7 +21307,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -21530,7 +21320,7 @@
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
@@ -21550,7 +21340,7 @@
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
@@ -21592,12 +21382,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -21631,17 +21421,17 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>0.420159730724297</v>
+        <v>0.005993712595487334</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -21661,7 +21451,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -21674,7 +21464,7 @@
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
@@ -21694,7 +21484,7 @@
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
@@ -21736,12 +21526,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -21785,7 +21575,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -21795,7 +21585,7 @@
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
@@ -21805,7 +21595,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -21813,42 +21603,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21880,12 +21670,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -21919,17 +21709,14 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.005993712595487334</v>
+        <v>0</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -21949,7 +21736,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -21957,42 +21744,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22024,12 +21811,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -22068,12 +21855,9 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -22083,7 +21867,7 @@
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
@@ -22093,7 +21877,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -22101,42 +21885,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22168,12 +21952,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -22309,12 +22093,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -22450,12 +22234,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -22591,12 +22375,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -22732,12 +22516,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -22873,12 +22657,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -23014,12 +22798,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -23155,12 +22939,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -23296,12 +23080,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -23437,12 +23221,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -23578,12 +23362,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -23719,12 +23503,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -23860,12 +23644,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -24001,12 +23785,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -24142,12 +23926,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -24283,12 +24067,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -24424,12 +24208,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -24565,12 +24349,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -24604,14 +24388,17 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.04736573491687511</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -24631,7 +24418,7 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT168" t="n">
@@ -24639,42 +24426,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -24706,12 +24493,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -24750,9 +24537,12 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -24772,7 +24562,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>HOLD_NZ_22077d3daa8999e7beacee412e5e</t>
+          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -24780,42 +24570,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -24847,12 +24637,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -24886,17 +24676,17 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>18</v>
+        <v>265</v>
       </c>
       <c r="O170" t="n">
-        <v>18</v>
+        <v>265</v>
       </c>
       <c r="R170" t="n">
-        <v>0.04736573491687511</v>
+        <v>1.28785025304921</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -24916,7 +24706,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TRIC_ANNUAL</t>
+          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -24929,7 +24719,7 @@
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
@@ -24949,7 +24739,7 @@
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
@@ -24991,12 +24781,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -25030,17 +24820,17 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>0.04912537187906513</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -25060,7 +24850,7 @@
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT171" t="n">
@@ -25073,7 +24863,7 @@
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
@@ -25093,7 +24883,7 @@
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
@@ -25135,12 +24925,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -25174,17 +24964,17 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>1.28785025304921</v>
+        <v>0</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -25204,7 +24994,7 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TRIC_ANNUAL</t>
+          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT172" t="n">
@@ -25217,7 +25007,7 @@
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
@@ -25237,7 +25027,7 @@
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
@@ -25279,12 +25069,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -25309,12 +25099,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-08-31</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N173" t="n">
@@ -25323,22 +25113,14 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="R173" t="n">
-        <v>0.04912537187906513</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -25348,582 +25130,53 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
+          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
         </is>
       </c>
       <c r="AT173" t="n">
         <v>1</v>
       </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>trichinellosis</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>旋毛虫病</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N174" t="n">
-        <v>1</v>
-      </c>
-      <c r="O174" t="n">
-        <v>1</v>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT174" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV174" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW174" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX174" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ174" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA174" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB174" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC174" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>trichinellosis</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>旋毛虫病</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
-      <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_TRIC_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT175" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW175" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX175" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ175" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA175" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB175" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC175" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>trichinellosis</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>旋毛虫病</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>2009-08-31</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>2009-08</t>
-        </is>
-      </c>
-      <c r="N176" t="n">
-        <v>1</v>
-      </c>
-      <c r="O176" t="n">
-        <v>1</v>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>HOLD_DE_56798495c355e79b09c37915f92f</t>
-        </is>
-      </c>
-      <c r="AT176" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV176" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW176" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX176" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ176" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA176" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB176" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC176" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -26055,7 +25308,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -26075,7 +25328,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -26085,7 +25338,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
